--- a/Luban/DataTables/Datas/__tables__.xlsx
+++ b/Luban/DataTables/Datas/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t>##var</t>
   </si>
@@ -110,13 +110,22 @@
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
   </si>
   <si>
-    <t>TestDemoMap</t>
+    <t>Test.TestDemoMap</t>
   </si>
   <si>
     <t>TestDemo</t>
   </si>
   <si>
-    <t>test_demo.xlsx</t>
+    <t>test.demo.xlsx</t>
+  </si>
+  <si>
+    <t>TTestMap</t>
+  </si>
+  <si>
+    <t>TTest</t>
+  </si>
+  <si>
+    <t>demo.tteess.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1058,8 +1067,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="3"/>
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4"/>
   <cols>
     <col min="2" max="2" width="20.375" customWidth="1"/>
     <col min="3" max="3" width="15.625" customWidth="1"/>
@@ -1172,6 +1181,20 @@
         <v>29</v>
       </c>
     </row>
+    <row r="5" customFormat="1" spans="1:11">
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Luban/DataTables/Datas/__tables__.xlsx
+++ b/Luban/DataTables/Datas/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
   <si>
     <t>##var</t>
   </si>
@@ -119,13 +119,16 @@
     <t>test.demo.xlsx</t>
   </si>
   <si>
-    <t>TTestMap</t>
-  </si>
-  <si>
-    <t>TTest</t>
-  </si>
-  <si>
-    <t>demo.tteess.xlsx</t>
+    <t>id+name</t>
+  </si>
+  <si>
+    <t>AchievementTable</t>
+  </si>
+  <si>
+    <t>AchievementData</t>
+  </si>
+  <si>
+    <t>Achievement@DesignPatternDataTable.xlsx</t>
   </si>
 </sst>
 </file>
@@ -741,11 +744,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1180,22 +1186,28 @@
       <c r="E4" t="s">
         <v>29</v>
       </c>
+      <c r="F4" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="5" customFormat="1" spans="1:11">
+    <row r="5" spans="1:11">
       <c r="B5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
       </c>
-      <c r="E5" t="s">
-        <v>32</v>
+      <c r="E5" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E5" r:id="rId1" display="Achievement@DesignPatternDataTable.xlsx"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/Luban/DataTables/Datas/__tables__.xlsx
+++ b/Luban/DataTables/Datas/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t>##var</t>
   </si>
@@ -119,16 +119,13 @@
     <t>test.demo.xlsx</t>
   </si>
   <si>
-    <t>id+name</t>
-  </si>
-  <si>
     <t>AchievementTable</t>
   </si>
   <si>
     <t>AchievementData</t>
   </si>
   <si>
-    <t>Achievement@DesignPatternDataTable.xlsx</t>
+    <t>Achievement_Career@DesignPatternDataTable.xlsx,Achievement_Battle@DesignPatternDataTable.xlsx,Achievement_Area@DesignPatternDataTable.xlsx</t>
   </si>
 </sst>
 </file>
@@ -744,14 +741,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1186,28 +1180,22 @@
       <c r="E4" t="s">
         <v>29</v>
       </c>
-      <c r="F4" t="s">
-        <v>30</v>
-      </c>
     </row>
     <row r="5" spans="1:11">
       <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
         <v>31</v>
-      </c>
-      <c r="C5" t="s">
-        <v>32</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>33</v>
+      <c r="E5" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="E5" r:id="rId1" display="Achievement@DesignPatternDataTable.xlsx"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
